--- a/results/04_final_refined_daily_hydroclimate_data/209/Wet_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/209/Wet_bulb_temp_06h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -427,8 +427,8 @@
       <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
-        <v>4</v>
+      <c r="D3">
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -455,8 +455,8 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5" t="s">
-        <v>4</v>
+      <c r="D5">
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -469,8 +469,8 @@
       <c r="C6">
         <v>5</v>
       </c>
-      <c r="D6" t="s">
-        <v>4</v>
+      <c r="D6">
+        <v>18.6</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -483,8 +483,8 @@
       <c r="C7">
         <v>6</v>
       </c>
-      <c r="D7" t="s">
-        <v>4</v>
+      <c r="D7">
+        <v>18.1</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -525,8 +525,8 @@
       <c r="C10">
         <v>9</v>
       </c>
-      <c r="D10" t="s">
-        <v>4</v>
+      <c r="D10">
+        <v>18.1</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -595,8 +595,8 @@
       <c r="C15">
         <v>14</v>
       </c>
-      <c r="D15" t="s">
-        <v>4</v>
+      <c r="D15">
+        <v>16.5</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -763,8 +763,8 @@
       <c r="C27">
         <v>26</v>
       </c>
-      <c r="D27" t="s">
-        <v>4</v>
+      <c r="D27">
+        <v>19.5</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -777,8 +777,8 @@
       <c r="C28">
         <v>27</v>
       </c>
-      <c r="D28" t="s">
-        <v>4</v>
+      <c r="D28">
+        <v>19.1</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -791,8 +791,8 @@
       <c r="C29">
         <v>28</v>
       </c>
-      <c r="D29" t="s">
-        <v>4</v>
+      <c r="D29">
+        <v>18.7</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -805,8 +805,8 @@
       <c r="C30">
         <v>29</v>
       </c>
-      <c r="D30" t="s">
-        <v>4</v>
+      <c r="D30">
+        <v>16.1</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -819,8 +819,8 @@
       <c r="C31">
         <v>30</v>
       </c>
-      <c r="D31" t="s">
-        <v>4</v>
+      <c r="D31">
+        <v>17.7</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -833,8 +833,8 @@
       <c r="C32">
         <v>31</v>
       </c>
-      <c r="D32" t="s">
-        <v>4</v>
+      <c r="D32">
+        <v>18.2</v>
       </c>
     </row>
   </sheetData>

--- a/results/04_final_refined_daily_hydroclimate_data/209/Wet_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/209/Wet_bulb_temp_06h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Year</t>
   </si>
@@ -26,9 +26,6 @@
   </si>
   <si>
     <t>Wet_bulb_temp_06h00</t>
-  </si>
-  <si>
-    <t>NaN</t>
   </si>
 </sst>
 </file>
@@ -497,8 +494,8 @@
       <c r="C8">
         <v>7</v>
       </c>
-      <c r="D8" t="s">
-        <v>4</v>
+      <c r="D8">
+        <v>19.3</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -511,8 +508,8 @@
       <c r="C9">
         <v>8</v>
       </c>
-      <c r="D9" t="s">
-        <v>4</v>
+      <c r="D9">
+        <v>18.8</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -539,8 +536,8 @@
       <c r="C11">
         <v>10</v>
       </c>
-      <c r="D11" t="s">
-        <v>4</v>
+      <c r="D11">
+        <v>19.1</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -553,8 +550,8 @@
       <c r="C12">
         <v>11</v>
       </c>
-      <c r="D12" t="s">
-        <v>4</v>
+      <c r="D12">
+        <v>17.7</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -567,8 +564,8 @@
       <c r="C13">
         <v>12</v>
       </c>
-      <c r="D13" t="s">
-        <v>4</v>
+      <c r="D13">
+        <v>18.2</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -581,8 +578,8 @@
       <c r="C14">
         <v>13</v>
       </c>
-      <c r="D14" t="s">
-        <v>4</v>
+      <c r="D14">
+        <v>18.8</v>
       </c>
     </row>
     <row r="15" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/209/Wet_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/209/Wet_bulb_temp_06h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -26,6 +26,9 @@
   </si>
   <si>
     <t>Wet_bulb_temp_06h00</t>
+  </si>
+  <si>
+    <t>NaN</t>
   </si>
 </sst>
 </file>
@@ -551,7 +554,7 @@
         <v>11</v>
       </c>
       <c r="D12">
-        <v>17.7</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -760,8 +763,8 @@
       <c r="C27">
         <v>26</v>
       </c>
-      <c r="D27">
-        <v>19.5</v>
+      <c r="D27" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -774,8 +777,8 @@
       <c r="C28">
         <v>27</v>
       </c>
-      <c r="D28">
-        <v>19.1</v>
+      <c r="D28" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -788,8 +791,8 @@
       <c r="C29">
         <v>28</v>
       </c>
-      <c r="D29">
-        <v>18.7</v>
+      <c r="D29" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -802,8 +805,8 @@
       <c r="C30">
         <v>29</v>
       </c>
-      <c r="D30">
-        <v>16.1</v>
+      <c r="D30" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -816,8 +819,8 @@
       <c r="C31">
         <v>30</v>
       </c>
-      <c r="D31">
-        <v>17.7</v>
+      <c r="D31" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -830,8 +833,8 @@
       <c r="C32">
         <v>31</v>
       </c>
-      <c r="D32">
-        <v>18.2</v>
+      <c r="D32" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/results/04_final_refined_daily_hydroclimate_data/209/Wet_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/209/Wet_bulb_temp_06h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Year</t>
   </si>
@@ -26,9 +26,6 @@
   </si>
   <si>
     <t>Wet_bulb_temp_06h00</t>
-  </si>
-  <si>
-    <t>NaN</t>
   </si>
 </sst>
 </file>
@@ -694,7 +691,7 @@
         <v>21</v>
       </c>
       <c r="D22">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -736,7 +733,7 @@
         <v>24</v>
       </c>
       <c r="D25">
-        <v>19.3</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -763,8 +760,8 @@
       <c r="C27">
         <v>26</v>
       </c>
-      <c r="D27" t="s">
-        <v>4</v>
+      <c r="D27">
+        <v>19.5</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -777,8 +774,8 @@
       <c r="C28">
         <v>27</v>
       </c>
-      <c r="D28" t="s">
-        <v>4</v>
+      <c r="D28">
+        <v>19.1</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -791,8 +788,8 @@
       <c r="C29">
         <v>28</v>
       </c>
-      <c r="D29" t="s">
-        <v>4</v>
+      <c r="D29">
+        <v>18.7</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -805,8 +802,8 @@
       <c r="C30">
         <v>29</v>
       </c>
-      <c r="D30" t="s">
-        <v>4</v>
+      <c r="D30">
+        <v>16.1</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -819,8 +816,8 @@
       <c r="C31">
         <v>30</v>
       </c>
-      <c r="D31" t="s">
-        <v>4</v>
+      <c r="D31">
+        <v>17.7</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -833,8 +830,8 @@
       <c r="C32">
         <v>31</v>
       </c>
-      <c r="D32" t="s">
-        <v>4</v>
+      <c r="D32">
+        <v>18.2</v>
       </c>
     </row>
   </sheetData>

--- a/results/04_final_refined_daily_hydroclimate_data/209/Wet_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/209/Wet_bulb_temp_06h00_timeseries.xlsx
@@ -411,7 +411,7 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>15.4</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -439,7 +439,7 @@
         <v>3</v>
       </c>
       <c r="D4">
-        <v>18.4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -481,7 +481,7 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>18.1</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -523,7 +523,7 @@
         <v>9</v>
       </c>
       <c r="D10">
-        <v>18.1</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -551,7 +551,7 @@
         <v>11</v>
       </c>
       <c r="D12">
-        <v>16.9</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -593,7 +593,7 @@
         <v>14</v>
       </c>
       <c r="D15">
-        <v>16.5</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -607,7 +607,7 @@
         <v>15</v>
       </c>
       <c r="D16">
-        <v>15.4</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -705,7 +705,7 @@
         <v>22</v>
       </c>
       <c r="D23">
-        <v>18.8</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -733,7 +733,7 @@
         <v>24</v>
       </c>
       <c r="D25">
-        <v>18.5</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="26" spans="1:4">
